--- a/synthetic/documents/eml/order_064_FCH-01063.xlsx
+++ b/synthetic/documents/eml/order_064_FCH-01063.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FreshClean Hospitality Group (SYNTHETIC)</t>
+          <t>Prime Corp. (SYNTHETIC)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Downtown Hotel</t>
+          <t>Prime Shipping Location 2</t>
         </is>
       </c>
     </row>
@@ -554,27 +554,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FST-FW-3816-ZN-B100</t>
+          <t>TLS-AWR-10IN-1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Flat Washer 3/8-16 Zinc</t>
+          <t>Adjustable Wrench 10in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>22.22</v>
+        <v>14.21</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>266.64</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="10">
@@ -583,16 +583,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>JAN-LNR-3340-05-BL</t>
+          <t>ADH-CON-126</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 33x40 0.5mil Black 250/CS</t>
+          <t>Construction Adhesive (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>35.61</v>
+        <v>60.43</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>213.66</v>
+        <v>483.44</v>
       </c>
     </row>
     <row r="11">
@@ -612,16 +612,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TAP-DT-2-BK</t>
+          <t>JAN-HSF-274</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Duct Tape Black 2 inch x 60 yd</t>
+          <t>Hand Soap Foam (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>23.44</v>
+        <v>82.47</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1125.12</v>
+        <v>329.88</v>
       </c>
     </row>
     <row r="12">
@@ -641,16 +641,16 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>JAN-LNR-3340-10-BL</t>
+          <t>ADH-CON-233</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 33x40 1.0mil Black 200/CS</t>
+          <t>Construction Adhesive (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>33.71</v>
+        <v>67.36</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>674.2</v>
+        <v>404.16</v>
       </c>
     </row>
     <row r="13">
@@ -670,12 +670,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>STOR-TOTE-27</t>
+          <t>JAN-LNR-4046-10-CL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Storage Tote 27 gallon with lid</t>
+          <t>Can Liner 40x46 1.0mil Clear (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -683,14 +683,14 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>14.69</v>
+        <v>37.07</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>176.28</v>
+        <v>444.84</v>
       </c>
     </row>
     <row r="14">
@@ -699,27 +699,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ELEC-EXT-25</t>
+          <t>PKG-PTC-202</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Extension Cord 25 ft 12/3 SJTW</t>
+          <t>Packing Tape Clear 2in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>30.48</v>
+        <v>60.96</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>304.8</v>
+        <v>365.76</v>
       </c>
     </row>
     <row r="15">
@@ -728,16 +728,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TOOL-HMR-CLW</t>
+          <t>TLS-TPM-16FT</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Claw Hammer 16 oz fiberglass</t>
+          <t>Tape Measure 16ft (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>15.17</v>
+        <v>12.71</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>60.68</v>
+        <v>101.68</v>
       </c>
     </row>
     <row r="16">
@@ -757,16 +757,16 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>LUB-WD40-11</t>
+          <t>LUB-POS-256</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>WD-40 Multi-Use 11 oz aerosol</t>
+          <t>Penetrating Oil Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>49.05</v>
+        <v>57.74</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>490.5</v>
+        <v>2771.52</v>
       </c>
     </row>
     <row r="17">
@@ -786,27 +786,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ABR-SAND-SHT-120</t>
+          <t>PKG-BBW-225</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Sandpaper Sheet 9x11 120 grit</t>
+          <t>Bubble Wrap 12in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>30.21</v>
+        <v>38.71</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>362.52</v>
+        <v>1858.08</v>
       </c>
     </row>
     <row r="18">
@@ -815,27 +815,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>STOR-BIN-LG</t>
+          <t>LUB-MPG-125</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Parts Bin Large 8x15x7</t>
+          <t>Multi-Purpose Grease (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>31.73</v>
+        <v>104.78</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>634.6</v>
+        <v>838.24</v>
       </c>
     </row>
     <row r="19">
@@ -844,27 +844,56 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TAP-WARN-TP-RW</t>
+          <t>TLS-UTB-091</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Danger Tape Red/White 3 inch x 1000 ft</t>
+          <t>Utility Blade Standard (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>65.25</v>
+        <v>9.34</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3132</v>
+        <v>74.72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>PPE-HAT-RED</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Hard Hat Red ANSI Type I (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>165.4</v>
       </c>
     </row>
   </sheetData>
